--- a/livrables/scenarios_parametres.xlsx
+++ b/livrables/scenarios_parametres.xlsx
@@ -430,7 +430,7 @@
   <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -515,7 +515,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -570,7 +570,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Dévers identique à S2 (norme CN trafic mixte) ; l'insuffisance 270 mm est propre au matériel pendulaire, sans effet sur le fret</t>
+          <t>Dévers identique au scénario recommandé (norme CN trafic mixte) ; l'insuffisance 270 mm est propre au matériel pendulaire, sans effet sur le fret</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Same cant as S2 (CN mixed-traffic standard); the 270 mm deficiency is specific to tilting equipment, no freight impact</t>
+          <t>Same cant as the recommended scenario (CN mixed-traffic standard); the 270 mm deficiency is specific to tilting equipment, no freight impact</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/livrables/scenarios_parametres.xlsx
+++ b/livrables/scenarios_parametres.xlsx
@@ -570,7 +570,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Dévers identique au scénario recommandé (norme CN trafic mixte) ; l'insuffisance 270 mm est propre au matériel pendulaire, sans effet sur le fret</t>
+          <t>Dévers identique au pendulaire des scénarios publiés (norme CN trafic mixte) ; l'insuffisance 270 mm est propre au matériel pendulaire, sans effet sur le fret</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Same cant as the recommended scenario (CN mixed-traffic standard); the 270 mm deficiency is specific to tilting equipment, no freight impact</t>
+          <t>Same cant as the published tilting scenarios (CN mixed-traffic standard); the 270 mm deficiency is specific to tilting equipment, no freight impact</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
